--- a/outputs/fifa_team_statistics/excel_por_categoria/Physical.xlsx
+++ b/outputs/fifa_team_statistics/excel_por_categoria/Physical.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Datos limpios" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Resumen numerico" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos limpios" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen numerico" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -540,20 +540,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6.25</v>
+        <v>6.22</v>
       </c>
       <c r="E4" t="n">
-        <v>4044</v>
+        <v>4280</v>
       </c>
       <c r="F4" t="n">
-        <v>1447</v>
+        <v>1492</v>
       </c>
       <c r="G4" t="n">
-        <v>344936.19</v>
+        <v>349040.82</v>
       </c>
     </row>
     <row r="5">
@@ -567,20 +567,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6.23</v>
+        <v>6.21</v>
       </c>
       <c r="E5" t="n">
-        <v>4388</v>
+        <v>5924</v>
       </c>
       <c r="F5" t="n">
-        <v>1513</v>
+        <v>2095</v>
       </c>
       <c r="G5" t="n">
-        <v>358610.48</v>
+        <v>505425.11</v>
       </c>
     </row>
     <row r="6">
@@ -594,20 +594,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6.22</v>
+        <v>6.21</v>
       </c>
       <c r="E6" t="n">
-        <v>4280</v>
+        <v>3766</v>
       </c>
       <c r="F6" t="n">
-        <v>1492</v>
+        <v>1251</v>
       </c>
       <c r="G6" t="n">
-        <v>349040.82</v>
+        <v>348567.52</v>
       </c>
     </row>
     <row r="7">
@@ -621,20 +621,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6.21</v>
+        <v>6.19</v>
       </c>
       <c r="E7" t="n">
-        <v>3766</v>
+        <v>5295</v>
       </c>
       <c r="F7" t="n">
-        <v>1251</v>
+        <v>1853</v>
       </c>
       <c r="G7" t="n">
-        <v>348567.52</v>
+        <v>464494.35</v>
       </c>
     </row>
     <row r="8">
@@ -648,20 +648,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6.19</v>
+        <v>6.17</v>
       </c>
       <c r="E8" t="n">
-        <v>5295</v>
+        <v>5775</v>
       </c>
       <c r="F8" t="n">
-        <v>1853</v>
+        <v>1993</v>
       </c>
       <c r="G8" t="n">
-        <v>464494.35</v>
+        <v>475647.91</v>
       </c>
     </row>
     <row r="9">
@@ -810,20 +810,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6.12</v>
+        <v>6.1</v>
       </c>
       <c r="E14" t="n">
-        <v>3592</v>
+        <v>3548</v>
       </c>
       <c r="F14" t="n">
-        <v>1283</v>
+        <v>1289</v>
       </c>
       <c r="G14" t="n">
-        <v>336456.49</v>
+        <v>350818.34</v>
       </c>
     </row>
     <row r="15">
@@ -837,20 +837,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>6.1</v>
+        <v>6.09</v>
       </c>
       <c r="E15" t="n">
-        <v>3548</v>
+        <v>3503</v>
       </c>
       <c r="F15" t="n">
-        <v>1289</v>
+        <v>1213</v>
       </c>
       <c r="G15" t="n">
-        <v>350818.34</v>
+        <v>333260.77</v>
       </c>
     </row>
     <row r="16">
@@ -864,20 +864,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Korea Republic</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>6.09</v>
       </c>
       <c r="E16" t="n">
-        <v>3503</v>
+        <v>3553</v>
       </c>
       <c r="F16" t="n">
-        <v>1213</v>
+        <v>1298</v>
       </c>
       <c r="G16" t="n">
-        <v>333260.77</v>
+        <v>334954.79</v>
       </c>
     </row>
     <row r="17">
@@ -891,20 +891,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Korea Republic</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>6.09</v>
       </c>
       <c r="E17" t="n">
-        <v>3553</v>
+        <v>3716</v>
       </c>
       <c r="F17" t="n">
-        <v>1298</v>
+        <v>1256</v>
       </c>
       <c r="G17" t="n">
-        <v>334954.79</v>
+        <v>342164.48</v>
       </c>
     </row>
     <row r="18">
@@ -918,20 +918,20 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>6.09</v>
       </c>
       <c r="E18" t="n">
-        <v>3716</v>
+        <v>5251</v>
       </c>
       <c r="F18" t="n">
-        <v>1256</v>
+        <v>1805</v>
       </c>
       <c r="G18" t="n">
-        <v>342164.48</v>
+        <v>451798.7</v>
       </c>
     </row>
     <row r="19">
@@ -945,20 +945,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>6.09</v>
       </c>
       <c r="E19" t="n">
-        <v>5251</v>
+        <v>3746</v>
       </c>
       <c r="F19" t="n">
-        <v>1805</v>
+        <v>1209</v>
       </c>
       <c r="G19" t="n">
-        <v>451798.7</v>
+        <v>328508.46</v>
       </c>
     </row>
     <row r="20">
@@ -972,20 +972,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>IR Iran</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>6.09</v>
+        <v>6.08</v>
       </c>
       <c r="E20" t="n">
-        <v>3746</v>
+        <v>4061</v>
       </c>
       <c r="F20" t="n">
-        <v>1209</v>
+        <v>1347</v>
       </c>
       <c r="G20" t="n">
-        <v>328508.46</v>
+        <v>344366.12</v>
       </c>
     </row>
     <row r="21">
@@ -999,20 +999,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>IR Iran</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>6.08</v>
+        <v>6.07</v>
       </c>
       <c r="E21" t="n">
-        <v>4061</v>
+        <v>4675</v>
       </c>
       <c r="F21" t="n">
-        <v>1347</v>
+        <v>1695</v>
       </c>
       <c r="G21" t="n">
-        <v>344366.12</v>
+        <v>444687.06</v>
       </c>
     </row>
     <row r="22">
@@ -1026,20 +1026,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>6.07</v>
       </c>
       <c r="E22" t="n">
-        <v>4675</v>
+        <v>3743</v>
       </c>
       <c r="F22" t="n">
-        <v>1695</v>
+        <v>1381</v>
       </c>
       <c r="G22" t="n">
-        <v>444687.06</v>
+        <v>334228.99</v>
       </c>
     </row>
     <row r="23">
@@ -1053,20 +1053,20 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>6.07</v>
+        <v>6.04</v>
       </c>
       <c r="E23" t="n">
-        <v>3743</v>
+        <v>3745</v>
       </c>
       <c r="F23" t="n">
-        <v>1381</v>
+        <v>1372</v>
       </c>
       <c r="G23" t="n">
-        <v>334228.99</v>
+        <v>336713.09</v>
       </c>
     </row>
     <row r="24">
@@ -1080,20 +1080,20 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>6.04</v>
       </c>
       <c r="E24" t="n">
-        <v>3745</v>
+        <v>4863</v>
       </c>
       <c r="F24" t="n">
-        <v>1372</v>
+        <v>1756</v>
       </c>
       <c r="G24" t="n">
-        <v>336713.09</v>
+        <v>453585</v>
       </c>
     </row>
     <row r="25">
@@ -1485,20 +1485,20 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>5.89</v>
+        <v>5.88</v>
       </c>
       <c r="E39" t="n">
-        <v>3738</v>
+        <v>3668</v>
       </c>
       <c r="F39" t="n">
-        <v>1411</v>
+        <v>1448</v>
       </c>
       <c r="G39" t="n">
-        <v>339841.4</v>
+        <v>337450.99</v>
       </c>
     </row>
     <row r="40">
@@ -1512,20 +1512,20 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D40" t="n">
         <v>5.88</v>
       </c>
       <c r="E40" t="n">
-        <v>3668</v>
+        <v>3395</v>
       </c>
       <c r="F40" t="n">
-        <v>1448</v>
+        <v>1260</v>
       </c>
       <c r="G40" t="n">
-        <v>337450.99</v>
+        <v>324019.59</v>
       </c>
     </row>
     <row r="41">
@@ -1539,20 +1539,20 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>5.88</v>
+        <v>5.86</v>
       </c>
       <c r="E41" t="n">
-        <v>3395</v>
+        <v>5363</v>
       </c>
       <c r="F41" t="n">
-        <v>1260</v>
+        <v>2010</v>
       </c>
       <c r="G41" t="n">
-        <v>324019.59</v>
+        <v>492777.45</v>
       </c>
     </row>
     <row r="42">
@@ -1787,12 +1787,12 @@
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -1879,10 +1879,10 @@
         <v>48</v>
       </c>
       <c r="C3" t="n">
-        <v>6.007291666666667</v>
+        <v>6.002916666666667</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1660010200344633</v>
+        <v>0.1630553793580226</v>
       </c>
       <c r="E3" t="n">
         <v>5.63</v>
@@ -1894,7 +1894,7 @@
         <v>6.02</v>
       </c>
       <c r="H3" t="n">
-        <v>6.12</v>
+        <v>6.105</v>
       </c>
       <c r="I3" t="n">
         <v>6.33</v>
@@ -1910,22 +1910,22 @@
         <v>48</v>
       </c>
       <c r="C4" t="n">
-        <v>4185.729166666667</v>
+        <v>4314.125</v>
       </c>
       <c r="D4" t="n">
-        <v>689.2848819558628</v>
+        <v>776.2031326859544</v>
       </c>
       <c r="E4" t="n">
         <v>3093</v>
       </c>
       <c r="F4" t="n">
-        <v>3660.5</v>
+        <v>3704</v>
       </c>
       <c r="G4" t="n">
-        <v>4042.5</v>
+        <v>4089</v>
       </c>
       <c r="H4" t="n">
-        <v>4661.5</v>
+        <v>4935</v>
       </c>
       <c r="I4" t="n">
         <v>5991</v>
@@ -1941,10 +1941,10 @@
         <v>48</v>
       </c>
       <c r="C5" t="n">
-        <v>1480.729166666667</v>
+        <v>1526.5625</v>
       </c>
       <c r="D5" t="n">
-        <v>262.8481269756547</v>
+        <v>295.2052950463529</v>
       </c>
       <c r="E5" t="n">
         <v>1080</v>
@@ -1953,13 +1953,13 @@
         <v>1274.75</v>
       </c>
       <c r="G5" t="n">
-        <v>1381</v>
+        <v>1414.5</v>
       </c>
       <c r="H5" t="n">
-        <v>1692.75</v>
+        <v>1783.25</v>
       </c>
       <c r="I5" t="n">
-        <v>2036</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="6">
@@ -1972,10 +1972,10 @@
         <v>48</v>
       </c>
       <c r="C6" t="n">
-        <v>376119.600625</v>
+        <v>387527.7445833334</v>
       </c>
       <c r="D6" t="n">
-        <v>58318.4547406101</v>
+        <v>64522.71284077767</v>
       </c>
       <c r="E6" t="n">
         <v>310036.75</v>
@@ -1984,10 +1984,10 @@
         <v>334773.34</v>
       </c>
       <c r="G6" t="n">
-        <v>345423.635</v>
+        <v>347946.355</v>
       </c>
       <c r="H6" t="n">
-        <v>441014.28</v>
+        <v>448960.625</v>
       </c>
       <c r="I6" t="n">
         <v>508926.8</v>

--- a/outputs/fifa_team_statistics/excel_por_categoria/Physical.xlsx
+++ b/outputs/fifa_team_statistics/excel_por_categoria/Physical.xlsx
@@ -426,50 +426,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Rank</t>
+          <t>Average Speed (km/h)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>High Speed Running</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Average Speed (km/h)</t>
+          <t>Sprints</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>High Speed Running</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Sprints</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Total Distance (m)</t>
         </is>
@@ -478,1297 +466,913 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Czechia</t>
-        </is>
+        <v>5.94</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3638</v>
       </c>
       <c r="D2" t="n">
-        <v>6.33</v>
+        <v>1240</v>
       </c>
       <c r="E2" t="n">
-        <v>4330</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1381</v>
-      </c>
-      <c r="G2" t="n">
-        <v>348826.43</v>
+        <v>330809.85</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
+        <v>5.71</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3329</v>
       </c>
       <c r="D3" t="n">
-        <v>6.29</v>
+        <v>1099</v>
       </c>
       <c r="E3" t="n">
-        <v>5991</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1990</v>
-      </c>
-      <c r="G3" t="n">
-        <v>508926.8</v>
+        <v>318655.05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>New Zealand</t>
-        </is>
+        <v>6.15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4023</v>
       </c>
       <c r="D4" t="n">
-        <v>6.22</v>
+        <v>1375</v>
       </c>
       <c r="E4" t="n">
-        <v>4280</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1492</v>
-      </c>
-      <c r="G4" t="n">
-        <v>349040.82</v>
+        <v>345911.08</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
+        <v>5.99</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3776</v>
       </c>
       <c r="D5" t="n">
-        <v>6.21</v>
+        <v>1274</v>
       </c>
       <c r="E5" t="n">
-        <v>5924</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2095</v>
-      </c>
-      <c r="G5" t="n">
-        <v>505425.11</v>
+        <v>341426.82</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Scotland</t>
-        </is>
+        <v>6.21</v>
+      </c>
+      <c r="C6" t="n">
+        <v>5924</v>
       </c>
       <c r="D6" t="n">
-        <v>6.21</v>
+        <v>2095</v>
       </c>
       <c r="E6" t="n">
-        <v>3766</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1251</v>
-      </c>
-      <c r="G6" t="n">
-        <v>348567.52</v>
+        <v>505425.11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Norway</t>
-        </is>
+        <v>6.04</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4863</v>
       </c>
       <c r="D7" t="n">
-        <v>6.19</v>
+        <v>1756</v>
       </c>
       <c r="E7" t="n">
-        <v>5295</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1853</v>
-      </c>
-      <c r="G7" t="n">
-        <v>464494.35</v>
+        <v>453585</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
+        <v>5.92</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4919</v>
       </c>
       <c r="D8" t="n">
-        <v>6.17</v>
+        <v>1705</v>
       </c>
       <c r="E8" t="n">
-        <v>5775</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1993</v>
-      </c>
-      <c r="G8" t="n">
-        <v>475647.91</v>
+        <v>448014.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
+        <v>5.97</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3419</v>
       </c>
       <c r="D9" t="n">
-        <v>6.15</v>
+        <v>1207</v>
       </c>
       <c r="E9" t="n">
-        <v>4023</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1375</v>
-      </c>
-      <c r="G9" t="n">
-        <v>345911.08</v>
+        <v>335193.42</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
+        <v>6.12</v>
+      </c>
+      <c r="C10" t="n">
+        <v>5536</v>
       </c>
       <c r="D10" t="n">
-        <v>6.14</v>
+        <v>2032</v>
       </c>
       <c r="E10" t="n">
-        <v>4068</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1515</v>
-      </c>
-      <c r="G10" t="n">
-        <v>346823.8</v>
+        <v>454227.11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
+        <v>5.63</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3289</v>
       </c>
       <c r="D11" t="n">
-        <v>6.13</v>
+        <v>1146</v>
       </c>
       <c r="E11" t="n">
-        <v>4296</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1363</v>
-      </c>
-      <c r="G11" t="n">
-        <v>347325.19</v>
+        <v>315670.95</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Congo DR</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
+        <v>5.96</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4983</v>
       </c>
       <c r="D12" t="n">
-        <v>6.13</v>
+        <v>1780</v>
       </c>
       <c r="E12" t="n">
-        <v>5111</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1964</v>
-      </c>
-      <c r="G12" t="n">
-        <v>455964.26</v>
+        <v>447455.88</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
+        <v>6.07</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3743</v>
       </c>
       <c r="D13" t="n">
-        <v>6.12</v>
+        <v>1381</v>
       </c>
       <c r="E13" t="n">
-        <v>5536</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2032</v>
-      </c>
-      <c r="G13" t="n">
-        <v>454227.11</v>
+        <v>334228.99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Türkiye</t>
-        </is>
+        <v>5.74</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3093</v>
       </c>
       <c r="D14" t="n">
-        <v>6.1</v>
+        <v>1230</v>
       </c>
       <c r="E14" t="n">
-        <v>3548</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1289</v>
-      </c>
-      <c r="G14" t="n">
-        <v>350818.34</v>
+        <v>315767.46</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Tunisia</t>
-        </is>
+        <v>6.33</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4330</v>
       </c>
       <c r="D15" t="n">
-        <v>6.09</v>
+        <v>1381</v>
       </c>
       <c r="E15" t="n">
-        <v>3503</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1213</v>
-      </c>
-      <c r="G15" t="n">
-        <v>333260.77</v>
+        <v>348826.43</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Korea Republic</t>
-        </is>
+        <v>5.81</v>
+      </c>
+      <c r="C16" t="n">
+        <v>4657</v>
       </c>
       <c r="D16" t="n">
-        <v>6.09</v>
+        <v>1692</v>
       </c>
       <c r="E16" t="n">
-        <v>3553</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1298</v>
-      </c>
-      <c r="G16" t="n">
-        <v>334954.79</v>
+        <v>434938.12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
+        <v>5.72</v>
+      </c>
+      <c r="C17" t="n">
+        <v>4598</v>
       </c>
       <c r="D17" t="n">
-        <v>6.09</v>
+        <v>1793</v>
       </c>
       <c r="E17" t="n">
-        <v>3716</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1256</v>
-      </c>
-      <c r="G17" t="n">
-        <v>342164.48</v>
+        <v>426982.84</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Mexico</t>
-        </is>
+        <v>6.14</v>
+      </c>
+      <c r="C18" t="n">
+        <v>4068</v>
       </c>
       <c r="D18" t="n">
-        <v>6.09</v>
+        <v>1515</v>
       </c>
       <c r="E18" t="n">
-        <v>5251</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1805</v>
-      </c>
-      <c r="G18" t="n">
-        <v>451798.7</v>
+        <v>346823.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>England</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Iraq</t>
-        </is>
+        <v>6.13</v>
+      </c>
+      <c r="C19" t="n">
+        <v>5111</v>
       </c>
       <c r="D19" t="n">
-        <v>6.09</v>
+        <v>1964</v>
       </c>
       <c r="E19" t="n">
-        <v>3746</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1209</v>
-      </c>
-      <c r="G19" t="n">
-        <v>328508.46</v>
+        <v>455964.26</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>19</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>IR Iran</t>
-        </is>
+        <v>6.07</v>
+      </c>
+      <c r="C20" t="n">
+        <v>4675</v>
       </c>
       <c r="D20" t="n">
-        <v>6.08</v>
+        <v>1695</v>
       </c>
       <c r="E20" t="n">
-        <v>4061</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1347</v>
-      </c>
-      <c r="G20" t="n">
-        <v>344366.12</v>
+        <v>444687.06</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
+        <v>6.29</v>
+      </c>
+      <c r="C21" t="n">
+        <v>5991</v>
       </c>
       <c r="D21" t="n">
-        <v>6.07</v>
+        <v>1990</v>
       </c>
       <c r="E21" t="n">
-        <v>4675</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1695</v>
-      </c>
-      <c r="G21" t="n">
-        <v>444687.06</v>
+        <v>508926.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>21</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Croatia</t>
-        </is>
+        <v>5.85</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3429</v>
       </c>
       <c r="D22" t="n">
-        <v>6.07</v>
+        <v>1275</v>
       </c>
       <c r="E22" t="n">
-        <v>3743</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1381</v>
-      </c>
-      <c r="G22" t="n">
-        <v>334228.99</v>
+        <v>331255.68</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>22</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Panama</t>
-        </is>
+        <v>5.96</v>
+      </c>
+      <c r="C23" t="n">
+        <v>3975</v>
       </c>
       <c r="D23" t="n">
-        <v>6.04</v>
+        <v>1376</v>
       </c>
       <c r="E23" t="n">
-        <v>3745</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1372</v>
-      </c>
-      <c r="G23" t="n">
-        <v>336713.09</v>
+        <v>334085.63</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>IR Iran</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>23</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Bosnia and Herzegovina</t>
-        </is>
+        <v>6.08</v>
+      </c>
+      <c r="C24" t="n">
+        <v>4061</v>
       </c>
       <c r="D24" t="n">
-        <v>6.04</v>
+        <v>1347</v>
       </c>
       <c r="E24" t="n">
-        <v>4863</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1756</v>
-      </c>
-      <c r="G24" t="n">
-        <v>453585</v>
+        <v>344366.12</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>24</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
+        <v>6.09</v>
+      </c>
+      <c r="C25" t="n">
+        <v>3746</v>
       </c>
       <c r="D25" t="n">
-        <v>6.02</v>
+        <v>1209</v>
       </c>
       <c r="E25" t="n">
-        <v>4678</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1669</v>
-      </c>
-      <c r="G25" t="n">
-        <v>446744.57</v>
+        <v>328508.46</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>25</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Saudi Arabia</t>
-        </is>
+        <v>6.02</v>
+      </c>
+      <c r="C26" t="n">
+        <v>4678</v>
       </c>
       <c r="D26" t="n">
-        <v>6.02</v>
+        <v>1669</v>
       </c>
       <c r="E26" t="n">
-        <v>4110</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1450</v>
-      </c>
-      <c r="G26" t="n">
-        <v>338484.3</v>
+        <v>446744.57</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>26</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
+        <v>6.13</v>
+      </c>
+      <c r="C27" t="n">
+        <v>4296</v>
       </c>
       <c r="D27" t="n">
-        <v>6</v>
+        <v>1363</v>
       </c>
       <c r="E27" t="n">
-        <v>4041</v>
-      </c>
-      <c r="F27" t="n">
-        <v>1348</v>
-      </c>
-      <c r="G27" t="n">
-        <v>334171.2</v>
+        <v>347325.19</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Korea Republic</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>27</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Paraguay</t>
-        </is>
+        <v>6.09</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3553</v>
       </c>
       <c r="D28" t="n">
-        <v>6</v>
+        <v>1298</v>
       </c>
       <c r="E28" t="n">
-        <v>5248</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1818</v>
-      </c>
-      <c r="G28" t="n">
-        <v>488152.5</v>
+        <v>334954.79</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>28</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Austria</t>
-        </is>
+        <v>6.09</v>
+      </c>
+      <c r="C29" t="n">
+        <v>5251</v>
       </c>
       <c r="D29" t="n">
-        <v>5.99</v>
+        <v>1805</v>
       </c>
       <c r="E29" t="n">
-        <v>3776</v>
-      </c>
-      <c r="F29" t="n">
-        <v>1274</v>
-      </c>
-      <c r="G29" t="n">
-        <v>341426.82</v>
+        <v>451798.7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>29</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Sweden</t>
-        </is>
+        <v>5.94</v>
+      </c>
+      <c r="C30" t="n">
+        <v>5228</v>
       </c>
       <c r="D30" t="n">
-        <v>5.99</v>
+        <v>2036</v>
       </c>
       <c r="E30" t="n">
-        <v>4426</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1586</v>
-      </c>
-      <c r="G30" t="n">
-        <v>439790.02</v>
+        <v>480903.65</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>30</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Cabo Verde</t>
-        </is>
+        <v>5.77</v>
+      </c>
+      <c r="C31" t="n">
+        <v>4601</v>
       </c>
       <c r="D31" t="n">
-        <v>5.97</v>
+        <v>1590</v>
       </c>
       <c r="E31" t="n">
-        <v>3419</v>
-      </c>
-      <c r="F31" t="n">
-        <v>1207</v>
-      </c>
-      <c r="G31" t="n">
-        <v>335193.42</v>
+        <v>455769.39</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>31</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Congo DR</t>
-        </is>
+        <v>6.22</v>
+      </c>
+      <c r="C32" t="n">
+        <v>4280</v>
       </c>
       <c r="D32" t="n">
-        <v>5.96</v>
+        <v>1492</v>
       </c>
       <c r="E32" t="n">
-        <v>4983</v>
-      </c>
-      <c r="F32" t="n">
-        <v>1780</v>
-      </c>
-      <c r="G32" t="n">
-        <v>447455.88</v>
+        <v>349040.82</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
+        <v>6.19</v>
+      </c>
+      <c r="C33" t="n">
+        <v>5295</v>
       </c>
       <c r="D33" t="n">
-        <v>5.96</v>
+        <v>1853</v>
       </c>
       <c r="E33" t="n">
-        <v>3975</v>
-      </c>
-      <c r="F33" t="n">
-        <v>1376</v>
-      </c>
-      <c r="G33" t="n">
-        <v>334085.63</v>
+        <v>464494.35</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>33</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Morocco</t>
-        </is>
+        <v>6.04</v>
+      </c>
+      <c r="C34" t="n">
+        <v>3745</v>
       </c>
       <c r="D34" t="n">
-        <v>5.94</v>
+        <v>1372</v>
       </c>
       <c r="E34" t="n">
-        <v>5228</v>
-      </c>
-      <c r="F34" t="n">
-        <v>2036</v>
-      </c>
-      <c r="G34" t="n">
-        <v>480903.65</v>
+        <v>336713.09</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>34</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="C35" t="n">
+        <v>5248</v>
       </c>
       <c r="D35" t="n">
-        <v>5.94</v>
+        <v>1818</v>
       </c>
       <c r="E35" t="n">
-        <v>3638</v>
-      </c>
-      <c r="F35" t="n">
-        <v>1240</v>
-      </c>
-      <c r="G35" t="n">
-        <v>330809.85</v>
+        <v>488152.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>35</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
+        <v>5.88</v>
+      </c>
+      <c r="C36" t="n">
+        <v>3395</v>
       </c>
       <c r="D36" t="n">
-        <v>5.92</v>
+        <v>1260</v>
       </c>
       <c r="E36" t="n">
-        <v>4919</v>
-      </c>
-      <c r="F36" t="n">
-        <v>1705</v>
-      </c>
-      <c r="G36" t="n">
-        <v>448014.6</v>
+        <v>324019.59</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>36</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Uzbekistan</t>
-        </is>
+        <v>5.64</v>
+      </c>
+      <c r="C37" t="n">
+        <v>3584</v>
       </c>
       <c r="D37" t="n">
-        <v>5.9</v>
+        <v>1080</v>
       </c>
       <c r="E37" t="n">
-        <v>3793</v>
-      </c>
-      <c r="F37" t="n">
-        <v>1354</v>
-      </c>
-      <c r="G37" t="n">
-        <v>337440.01</v>
+        <v>310036.75</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>37</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
+        <v>6.02</v>
+      </c>
+      <c r="C38" t="n">
+        <v>4110</v>
       </c>
       <c r="D38" t="n">
-        <v>5.9</v>
+        <v>1450</v>
       </c>
       <c r="E38" t="n">
-        <v>5039</v>
-      </c>
-      <c r="F38" t="n">
-        <v>1884</v>
-      </c>
-      <c r="G38" t="n">
-        <v>429068.84</v>
+        <v>338484.3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>38</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Uruguay</t>
-        </is>
+        <v>6.21</v>
+      </c>
+      <c r="C39" t="n">
+        <v>3766</v>
       </c>
       <c r="D39" t="n">
-        <v>5.88</v>
+        <v>1251</v>
       </c>
       <c r="E39" t="n">
-        <v>3668</v>
-      </c>
-      <c r="F39" t="n">
-        <v>1448</v>
-      </c>
-      <c r="G39" t="n">
-        <v>337450.99</v>
+        <v>348567.52</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>39</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
+        <v>5.86</v>
+      </c>
+      <c r="C40" t="n">
+        <v>5363</v>
       </c>
       <c r="D40" t="n">
-        <v>5.88</v>
+        <v>2010</v>
       </c>
       <c r="E40" t="n">
-        <v>3395</v>
-      </c>
-      <c r="F40" t="n">
-        <v>1260</v>
-      </c>
-      <c r="G40" t="n">
-        <v>324019.59</v>
+        <v>492777.45</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>40</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Senegal</t>
-        </is>
+        <v>5.9</v>
+      </c>
+      <c r="C41" t="n">
+        <v>5039</v>
       </c>
       <c r="D41" t="n">
-        <v>5.86</v>
+        <v>1884</v>
       </c>
       <c r="E41" t="n">
-        <v>5363</v>
-      </c>
-      <c r="F41" t="n">
-        <v>2010</v>
-      </c>
-      <c r="G41" t="n">
-        <v>492777.45</v>
+        <v>429068.84</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>41</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ghana</t>
-        </is>
+        <v>6.09</v>
+      </c>
+      <c r="C42" t="n">
+        <v>3716</v>
       </c>
       <c r="D42" t="n">
-        <v>5.85</v>
+        <v>1256</v>
       </c>
       <c r="E42" t="n">
-        <v>3429</v>
-      </c>
-      <c r="F42" t="n">
-        <v>1275</v>
-      </c>
-      <c r="G42" t="n">
-        <v>331255.68</v>
+        <v>342164.48</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>42</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Côte d'Ivoire</t>
-        </is>
+        <v>5.99</v>
+      </c>
+      <c r="C43" t="n">
+        <v>4426</v>
       </c>
       <c r="D43" t="n">
-        <v>5.81</v>
+        <v>1586</v>
       </c>
       <c r="E43" t="n">
-        <v>4657</v>
-      </c>
-      <c r="F43" t="n">
-        <v>1692</v>
-      </c>
-      <c r="G43" t="n">
-        <v>434938.12</v>
+        <v>439790.02</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>43</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="C44" t="n">
+        <v>4041</v>
       </c>
       <c r="D44" t="n">
-        <v>5.77</v>
+        <v>1348</v>
       </c>
       <c r="E44" t="n">
-        <v>4601</v>
-      </c>
-      <c r="F44" t="n">
-        <v>1590</v>
-      </c>
-      <c r="G44" t="n">
-        <v>455769.39</v>
+        <v>334171.2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>44</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Curaçao</t>
-        </is>
+        <v>6.09</v>
+      </c>
+      <c r="C45" t="n">
+        <v>3503</v>
       </c>
       <c r="D45" t="n">
-        <v>5.74</v>
+        <v>1213</v>
       </c>
       <c r="E45" t="n">
-        <v>3093</v>
-      </c>
-      <c r="F45" t="n">
-        <v>1230</v>
-      </c>
-      <c r="G45" t="n">
-        <v>315767.46</v>
+        <v>333260.77</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>45</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ecuador</t>
-        </is>
+        <v>6.1</v>
+      </c>
+      <c r="C46" t="n">
+        <v>3548</v>
       </c>
       <c r="D46" t="n">
-        <v>5.72</v>
+        <v>1289</v>
       </c>
       <c r="E46" t="n">
-        <v>4598</v>
-      </c>
-      <c r="F46" t="n">
-        <v>1793</v>
-      </c>
-      <c r="G46" t="n">
-        <v>426982.84</v>
+        <v>350818.34</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>46</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
+        <v>6.17</v>
+      </c>
+      <c r="C47" t="n">
+        <v>5775</v>
       </c>
       <c r="D47" t="n">
-        <v>5.71</v>
+        <v>1993</v>
       </c>
       <c r="E47" t="n">
-        <v>3329</v>
-      </c>
-      <c r="F47" t="n">
-        <v>1099</v>
-      </c>
-      <c r="G47" t="n">
-        <v>318655.05</v>
+        <v>475647.91</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>47</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
+        <v>5.88</v>
+      </c>
+      <c r="C48" t="n">
+        <v>3668</v>
       </c>
       <c r="D48" t="n">
-        <v>5.64</v>
+        <v>1448</v>
       </c>
       <c r="E48" t="n">
-        <v>3584</v>
-      </c>
-      <c r="F48" t="n">
-        <v>1080</v>
-      </c>
-      <c r="G48" t="n">
-        <v>310036.75</v>
+        <v>337450.99</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>48</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
+        <v>5.9</v>
+      </c>
+      <c r="C49" t="n">
+        <v>3793</v>
       </c>
       <c r="D49" t="n">
-        <v>5.63</v>
+        <v>1354</v>
       </c>
       <c r="E49" t="n">
-        <v>3289</v>
-      </c>
-      <c r="F49" t="n">
-        <v>1146</v>
-      </c>
-      <c r="G49" t="n">
-        <v>315670.95</v>
+        <v>337440.01</v>
       </c>
     </row>
   </sheetData>
@@ -1782,7 +1386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1841,155 +1445,124 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Rank</t>
+          <t>Average Speed (km/h)</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>48</v>
       </c>
       <c r="C2" t="n">
-        <v>24.5</v>
+        <v>6.002916666666667</v>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>0.1630553793580226</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>5.63</v>
       </c>
       <c r="F2" t="n">
-        <v>12.75</v>
+        <v>5.9</v>
       </c>
       <c r="G2" t="n">
-        <v>24.5</v>
+        <v>6.02</v>
       </c>
       <c r="H2" t="n">
-        <v>36.25</v>
+        <v>6.105</v>
       </c>
       <c r="I2" t="n">
-        <v>48</v>
+        <v>6.33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Average Speed (km/h)</t>
+          <t>High Speed Running</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>48</v>
       </c>
       <c r="C3" t="n">
-        <v>6.002916666666667</v>
+        <v>4314.125</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1630553793580226</v>
+        <v>776.2031326859544</v>
       </c>
       <c r="E3" t="n">
-        <v>5.63</v>
+        <v>3093</v>
       </c>
       <c r="F3" t="n">
-        <v>5.9</v>
+        <v>3704</v>
       </c>
       <c r="G3" t="n">
-        <v>6.02</v>
+        <v>4089</v>
       </c>
       <c r="H3" t="n">
-        <v>6.105</v>
+        <v>4935</v>
       </c>
       <c r="I3" t="n">
-        <v>6.33</v>
+        <v>5991</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>High Speed Running</t>
+          <t>Sprints</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>48</v>
       </c>
       <c r="C4" t="n">
-        <v>4314.125</v>
+        <v>1526.5625</v>
       </c>
       <c r="D4" t="n">
-        <v>776.2031326859544</v>
+        <v>295.2052950463529</v>
       </c>
       <c r="E4" t="n">
-        <v>3093</v>
+        <v>1080</v>
       </c>
       <c r="F4" t="n">
-        <v>3704</v>
+        <v>1274.75</v>
       </c>
       <c r="G4" t="n">
-        <v>4089</v>
+        <v>1414.5</v>
       </c>
       <c r="H4" t="n">
-        <v>4935</v>
+        <v>1783.25</v>
       </c>
       <c r="I4" t="n">
-        <v>5991</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Sprints</t>
+          <t>Total Distance (m)</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>48</v>
       </c>
       <c r="C5" t="n">
-        <v>1526.5625</v>
+        <v>387527.7445833334</v>
       </c>
       <c r="D5" t="n">
-        <v>295.2052950463529</v>
+        <v>64522.71284077767</v>
       </c>
       <c r="E5" t="n">
-        <v>1080</v>
+        <v>310036.75</v>
       </c>
       <c r="F5" t="n">
-        <v>1274.75</v>
+        <v>334773.34</v>
       </c>
       <c r="G5" t="n">
-        <v>1414.5</v>
+        <v>347946.355</v>
       </c>
       <c r="H5" t="n">
-        <v>1783.25</v>
+        <v>448960.625</v>
       </c>
       <c r="I5" t="n">
-        <v>2095</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Total Distance (m)</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>48</v>
-      </c>
-      <c r="C6" t="n">
-        <v>387527.7445833334</v>
-      </c>
-      <c r="D6" t="n">
-        <v>64522.71284077767</v>
-      </c>
-      <c r="E6" t="n">
-        <v>310036.75</v>
-      </c>
-      <c r="F6" t="n">
-        <v>334773.34</v>
-      </c>
-      <c r="G6" t="n">
-        <v>347946.355</v>
-      </c>
-      <c r="H6" t="n">
-        <v>448960.625</v>
-      </c>
-      <c r="I6" t="n">
         <v>508926.8</v>
       </c>
     </row>

--- a/outputs/fifa_team_statistics/excel_por_categoria/Physical.xlsx
+++ b/outputs/fifa_team_statistics/excel_por_categoria/Physical.xlsx
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.99</v>
+        <v>6.04</v>
       </c>
       <c r="C5" t="n">
         <v>3776</v>
@@ -536,7 +536,7 @@
         <v>1274</v>
       </c>
       <c r="E5" t="n">
-        <v>341426.82</v>
+        <v>454301.2</v>
       </c>
     </row>
     <row r="6">
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>6.09</v>
+        <v>6.12</v>
       </c>
       <c r="C42" t="n">
         <v>3716</v>
@@ -1239,7 +1239,7 @@
         <v>1256</v>
       </c>
       <c r="E42" t="n">
-        <v>342164.48</v>
+        <v>456675.76</v>
       </c>
     </row>
     <row r="43">
@@ -1392,10 +1392,10 @@
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
   </cols>
@@ -1452,10 +1452,10 @@
         <v>48</v>
       </c>
       <c r="C2" t="n">
-        <v>6.002916666666667</v>
+        <v>6.004583333333334</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1630553793580226</v>
+        <v>0.1635244575803582</v>
       </c>
       <c r="E2" t="n">
         <v>5.63</v>
@@ -1464,10 +1464,10 @@
         <v>5.9</v>
       </c>
       <c r="G2" t="n">
-        <v>6.02</v>
+        <v>6.029999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>6.105</v>
+        <v>6.12</v>
       </c>
       <c r="I2" t="n">
         <v>6.33</v>
@@ -1545,10 +1545,10 @@
         <v>48</v>
       </c>
       <c r="C5" t="n">
-        <v>387527.7445833334</v>
+        <v>392264.9458333333</v>
       </c>
       <c r="D5" t="n">
-        <v>64522.71284077767</v>
+        <v>65175.59455941422</v>
       </c>
       <c r="E5" t="n">
         <v>310036.75</v>
@@ -1557,10 +1557,10 @@
         <v>334773.34</v>
       </c>
       <c r="G5" t="n">
-        <v>347946.355</v>
+        <v>348933.625</v>
       </c>
       <c r="H5" t="n">
-        <v>448960.625</v>
+        <v>453745.5275</v>
       </c>
       <c r="I5" t="n">
         <v>508926.8</v>
